--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3846153846153846</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="B2">
-        <v>0.1764705882352941</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5070422535211268</v>
+        <v>0.2887323943661972</v>
       </c>
       <c r="D2">
-        <v>0.6481481481481481</v>
+        <v>0.7829457364341085</v>
       </c>
       <c r="E2">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2413793103448276</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2887323943661972</v>
+        <v>0.3169014084507042</v>
       </c>
       <c r="D2">
-        <v>0.7829457364341085</v>
+        <v>0.7461538461538462</v>
       </c>
       <c r="E2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F2">
         <v>13</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
